--- a/validation/validation table.xlsx
+++ b/validation/validation table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos Paja Suarez\PycharmProjects\imoc_pdac\validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2525CC5-8D30-4597-84D8-ACC036BA262C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9414ADDF-7F38-4B18-955E-2C3D77E70D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7ED0CA7C-D63E-44BF-B766-BEDBB691729B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>Cohort</t>
   </si>
@@ -51,30 +51,9 @@
     <t>Clinical Proteomic Tumor Analysis Consortium (CPTAC)</t>
   </si>
   <si>
-    <t>RNAseq, Proteome, Phosphoproteome, N-glycoproteome, O-glycoproteome, Methylation, SCNV, MicroRNA, circRNA, Mutation</t>
-  </si>
-  <si>
-    <t>https://linkedomics.org/data_download/CPTAC-PDAC/</t>
-  </si>
-  <si>
     <t>Modalities available</t>
   </si>
   <si>
-    <t>Modalities used</t>
-  </si>
-  <si>
-    <t>RNAseq, Methylation, SCNV</t>
-  </si>
-  <si>
-    <t>Results</t>
-  </si>
-  <si>
-    <t>140 (5 missing survival data, so 135)</t>
-  </si>
-  <si>
-    <t>GISTIC2.0 was performed on SCNV data to obtain arm-level data, similar to the one used in our manuscript. The methylation data contained 1/3 biomarkers reported, and the arm-level CN data had 3/4 biomarkers. Due to missing one CN biomarker, model was not able to run. RNAseq data and associated genes for every biomarker were used instead (see "Associated genes" sheet).</t>
-  </si>
-  <si>
     <t>Biomarker</t>
   </si>
   <si>
@@ -132,9 +111,6 @@
     <t>Genes used in validation (available in dataset)</t>
   </si>
   <si>
-    <t>Link to data</t>
-  </si>
-  <si>
     <t>LINC01670, LINC03104, CTBP2P10, LINC03105, CTBP2P9, MIR6724-1, MIR3648-1, RNA5-8SN2, MIR6724-2, MIR6724-3, RNA5-8SN3, MIR6724-4, RNA5-8SN1, RPSAP68, LINC01666, SNX18P10, MTCO1P1, MIR3648-2, TEKT4P2, CDRT15P9, TEKT4P2, SOWAHCP2, SNX18P12, NCOR1P4, LINC01667, RN7SL52P, CDRT15P8, EIF3FP1, VN1R7P, BAGE2, TPTE, CYCSP41, SLC25A15P4, IGHV1OR21-1, ANKRD30BP2, RNU6-614P, ZNF355P, BNIP3P43, FGF7P2, ANKRD30BP1, MIR3156-3, GTF2IP2, VN1R8P, LINC01674, SNX19P1, OR4K11P, OR4K12P, POTED, RNU6-286P, MIR3118-1, GRAMD4P1, CXADRP1, LONRF2P5, MIR8069, FEM1AP1, TERF1P1, FAM207CP, GXYLT1P2, CNN2P7, ZNF114P1, CYP4F29P, SNX18P13, ANKRD20A11P, RHOT1P2, RNU6-954P, NF1P3, PPP6R2P1, FRG2MP, ANKRD20A18P, RNA5SP488, LIPI, ERLEC1P1, RBM11, ABCC13, HSPA13, SAMSN1, SAMSN1-AS1, POLR2CP1, GAPDHP16, ASMER1, RBMX2P1, NRIP1, LINC02920, CYCSP42, RNU6-1326P, RAD23BP3, USP25, RBPMSLP</t>
   </si>
   <si>
@@ -144,51 +120,76 @@
     <t xml:space="preserve">* selected 3 random genes available in the dataset </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Clusters were calculated for every biomarker by grouping patients depending on the expression levels of the gene: high expression = expression &gt; mean expression for that gene. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RMST:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Significance in MAP2K4 (17p12) after 18m and overall. LINC01667 and TEKT4P2 (21q11.2) significance from 1.5-2y and borderline values up to for 6m and 1y, respectively. TBX2 (cg07095230) significant at all timepoints. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LOG-RANK:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> MAP2K4 (17p12) significance after 18m and overall. LINC01667 (21q11.2) significance after 18m and overall. TBX2 (cg07095230) significant at all timepoints.</t>
-    </r>
+    <t>RNAseq, somatic mutation, CNV, methylation, miRNA, circRNA, gene fusion, proteomics, phosphoproteomics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methylation data recorded at gene-level (average of several probes associated with gene) instead of probe-level. SCNV data recorded at gene-level, but contains cytoband information. </t>
+  </si>
+  <si>
+    <t>Mutations, CNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restricted access (controlled data). ICGC Data Portal closed. </t>
+  </si>
+  <si>
+    <t>International Cancer Genome Consortium (ICGC)</t>
+  </si>
+  <si>
+    <t>PRINCE Trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNAseq </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focus on results from drug treatment rather than tumor characteristics. </t>
+  </si>
+  <si>
+    <t>MSK-IMPACT</t>
+  </si>
+  <si>
+    <t>Mutations, CNV, structural variants</t>
+  </si>
+  <si>
+    <t>Mutations, RNAseq</t>
+  </si>
+  <si>
+    <t>Only data from 96 samples in RNAseq</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>UTSW, Nat Commun 2015</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/25855536/</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/35662283/</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/23103869/</t>
+  </si>
+  <si>
+    <t>https://www.mskcc.org/msk-impact</t>
+  </si>
+  <si>
+    <t>QCMG, Nature 2016</t>
+  </si>
+  <si>
+    <t>MSK, J Natl Cancer Inst 2025</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40511613/</t>
+  </si>
+  <si>
+    <t>ctDNA data</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/26909576/</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/34534465/</t>
   </si>
 </sst>
 </file>
@@ -226,12 +227,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -256,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -274,12 +281,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -300,9 +317,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -340,7 +357,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -446,7 +463,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -596,19 +613,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA5B12CD-C45E-4020-B04E-B2D625E5A757}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="95" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="98.77734375" customWidth="1"/>
-    <col min="7" max="7" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.6640625" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -616,118 +631,155 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="7">
+        <v>140</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B3" s="3">
+        <v>90</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3">
+        <v>93</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="3">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
+      <c r="E5" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3">
+        <v>456</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3">
+        <v>109</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E7" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3">
+        <v>397</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{56C44A86-4FC4-4813-A716-E187D273F5F8}"/>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{B9EEB635-B2D8-4D1D-8D7E-BC06048D77C9}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{8A40762D-A3FE-48F2-9F0F-CBF7C5B158CD}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{4B8490DF-B0BA-4F86-87AD-C7BAC8A5807F}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{02BBBD1F-6869-4D4E-9094-84BA2A242769}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{8844E8B6-54B9-4F48-93CA-750F37D033E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -745,102 +797,102 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
